--- a/support/specifications/hl7/HL7v2.to.FHIR.Conversion.Spec.xlsx
+++ b/support/specifications/hl7/HL7v2.to.FHIR.Conversion.Spec.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12180" tabRatio="753" firstSheet="1" activeTab="5"/>
+    <workbookView windowWidth="19200" windowHeight="8000" tabRatio="753" firstSheet="1" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="Info" sheetId="1" r:id="rId1"/>
@@ -511,11 +511,23 @@
     <t>"meta" : {
     "lastUpdated" : "2024-02-23T00:00:00Z",
     "profile" : ["http://shinny.org/us/ny/hrsn/StructureDefinition/SHINNYBundleProfile"],
-    "security": [ {
-                  "code": "ETH",
-                  "system": "http://terminology.hl7.org/CodeSystem/v3-ActCode",
-                  "display": "Substance abuse information sensitivity"
-              } ]
+   "security": [
+      {
+        "code": "ETH",
+        "system": "http://terminology.hl7.org/CodeSystem/v3-ActCode",
+        "display": "Substance abuse information sensitivity"
+      },
+      {
+        "code": "MH",
+        "system": "http://terminology.hl7.org/CodeSystem/v3-ActCode",
+        "display": "Mental health information sensitivity"
+      },
+      {
+        "code": "DVD",
+        "system": "http://terminology.hl7.org/CodeSystem/v3-ActCode",
+        "display": "Developmental disability information sensitivity"
+      }
+    ],
   },</t>
   </si>
   <si>
@@ -529,13 +541,6 @@
   </si>
   <si>
     <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF00B050"/>
-        <rFont val="Calibri"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
       <t>If the header variable `</t>
     </r>
     <r>
@@ -578,7 +583,51 @@
         <charset val="134"/>
         <scheme val="minor"/>
       </rPr>
-      <t>', then only the meta -&gt; security will be added.</t>
+      <t>', then the 'ETH' code will be added to meta -&gt; security.
+If the header variable `</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF00B050"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>X-TechBD-OPWDD</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF00B050"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>` has the value 'True', then the 'DVD' code will be added to meta -&gt; security.
+If the header variable `</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF00B050"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>X-TechBD-OMH</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF00B050"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>` has the value 'True', then the 'MH' code will be added to meta -&gt; security.</t>
     </r>
   </si>
   <si>
@@ -848,6 +897,15 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <b/>
+        <u/>
+        <sz val="11"/>
+        <color rgb="FF00B050"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t>PID.11.7 -&gt; use Mapping</t>
     </r>
     <r>
@@ -3865,6 +3923,15 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <b/>
+        <u/>
+        <sz val="11"/>
+        <color rgb="FF00B050"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t>ORC.22.7 -&gt; use Mapping</t>
     </r>
     <r>
@@ -5419,14 +5486,15 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color indexed="8"/>
+      <color rgb="FFC00000"/>
       <name val="Calibri"/>
       <charset val="134"/>
+      <scheme val="minor"/>
     </font>
     <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FF00B050"/>
+      <color indexed="8"/>
       <name val="Calibri"/>
       <charset val="134"/>
     </font>
@@ -5439,19 +5507,18 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFC00000"/>
+      <u/>
+      <sz val="10"/>
+      <color rgb="FF00B050"/>
       <name val="Calibri"/>
       <charset val="134"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <b/>
       <sz val="11"/>
+      <color rgb="FF00B050"/>
       <name val="Calibri"/>
       <charset val="134"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <b/>
@@ -5467,11 +5534,11 @@
       <charset val="134"/>
     </font>
     <font>
-      <u/>
-      <sz val="10"/>
-      <color rgb="FF00B050"/>
+      <b/>
+      <sz val="11"/>
       <name val="Calibri"/>
       <charset val="134"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="40">
@@ -5999,7 +6066,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="69">
+  <cellXfs count="73">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -6192,6 +6259,9 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
@@ -6200,6 +6270,15 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -6226,7 +6305,7 @@
     <cellStyle name="Note" xfId="8" builtinId="10"/>
     <cellStyle name="Warning Text" xfId="9" builtinId="11"/>
     <cellStyle name="Title" xfId="10" builtinId="15"/>
-    <cellStyle name="CExplanatory Text" xfId="11" builtinId="53"/>
+    <cellStyle name="Explanatory Text" xfId="11" builtinId="53"/>
     <cellStyle name="Heading 1" xfId="12" builtinId="16"/>
     <cellStyle name="Heading 2" xfId="13" builtinId="17"/>
     <cellStyle name="Heading 3" xfId="14" builtinId="18"/>
@@ -6277,7 +6356,7 @@
     <cellStyle name="Warning" xfId="59"/>
   </cellStyles>
   <tableStyles count="1" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16">
-    <tableStyle name="Invisible" pivot="0" table="0" count="0" xr9:uid="{E3B77C8E-14A8-4A8F-831C-BD0090FCDAAF}"/>
+    <tableStyle name="Invisible" pivot="0" table="0" count="0" xr9:uid="{8B1909D0-06DC-4F3F-96EE-CF8F1486C37B}"/>
   </tableStyles>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -6546,23 +6625,23 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:C8"/>
-  <sheetFormatPr defaultColWidth="11.8571428571429" defaultRowHeight="15" outlineLevelRow="7" outlineLevelCol="2"/>
+  <sheetFormatPr defaultColWidth="11.8545454545455" defaultRowHeight="14.5" outlineLevelRow="7" outlineLevelCol="2"/>
   <cols>
-    <col min="1" max="1" width="14.2857142857143" style="68" customWidth="1"/>
+    <col min="1" max="1" width="14.2818181818182" style="72" customWidth="1"/>
     <col min="2" max="2" width="47" customWidth="1"/>
-    <col min="3" max="3" width="123.571428571429" customWidth="1"/>
+    <col min="3" max="3" width="123.572727272727" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
-      <c r="A1" s="65" t="s">
+      <c r="A1" s="66" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="64"/>
-      <c r="C1" s="64"/>
+      <c r="B1" s="65"/>
+      <c r="C1" s="65"/>
     </row>
     <row r="2" spans="1:3">
-      <c r="A2" s="64"/>
-      <c r="B2" s="64" t="s">
+      <c r="A2" s="65"/>
+      <c r="B2" s="65" t="s">
         <v>1</v>
       </c>
       <c r="C2" s="57" t="s">
@@ -6570,8 +6649,8 @@
       </c>
     </row>
     <row r="3" spans="1:3">
-      <c r="A3" s="64"/>
-      <c r="B3" s="64" t="s">
+      <c r="A3" s="65"/>
+      <c r="B3" s="65" t="s">
         <v>3</v>
       </c>
       <c r="C3" s="57" t="s">
@@ -6579,26 +6658,26 @@
       </c>
     </row>
     <row r="4" spans="1:3">
-      <c r="A4" s="64"/>
-      <c r="B4" s="64" t="s">
+      <c r="A4" s="65"/>
+      <c r="B4" s="65" t="s">
         <v>5</v>
       </c>
       <c r="C4" s="57" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="5" ht="45" spans="1:3">
-      <c r="A5" s="64"/>
-      <c r="B5" s="64" t="s">
+    <row r="5" ht="43.5" spans="1:3">
+      <c r="A5" s="65"/>
+      <c r="B5" s="65" t="s">
         <v>7</v>
       </c>
-      <c r="C5" s="67" t="s">
+      <c r="C5" s="71" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="6" spans="1:3">
-      <c r="A6" s="64"/>
-      <c r="B6" s="67" t="s">
+      <c r="A6" s="65"/>
+      <c r="B6" s="71" t="s">
         <v>9</v>
       </c>
       <c r="C6" s="57" t="s">
@@ -6606,17 +6685,17 @@
       </c>
     </row>
     <row r="7" spans="1:3">
-      <c r="A7" s="64"/>
-      <c r="B7" s="64" t="s">
+      <c r="A7" s="65"/>
+      <c r="B7" s="65" t="s">
         <v>11</v>
       </c>
       <c r="C7" s="12" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="8" spans="1:2">
-      <c r="A8" s="64"/>
-      <c r="B8" s="64"/>
+    <row r="8" spans="1:3">
+      <c r="A8" s="65"/>
+      <c r="B8" s="65"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1.39370078740157" bottom="1.39370078740157" header="1" footer="1"/>
@@ -6629,15 +6708,15 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:F21"/>
-  <sheetFormatPr defaultColWidth="9.14285714285714" defaultRowHeight="15" outlineLevelCol="5"/>
+  <sheetFormatPr defaultColWidth="9.14545454545454" defaultRowHeight="14.5" outlineLevelCol="5"/>
   <cols>
-    <col min="1" max="1" width="14.7142857142857" style="2" customWidth="1"/>
-    <col min="2" max="2" width="33.5714285714286" style="2" customWidth="1"/>
-    <col min="3" max="3" width="49.6666666666667" style="2" customWidth="1"/>
-    <col min="4" max="4" width="56.552380952381" style="2" customWidth="1"/>
-    <col min="5" max="5" width="53.2857142857143" style="2" customWidth="1"/>
-    <col min="6" max="6" width="47.5714285714286" style="2" customWidth="1"/>
-    <col min="7" max="16384" width="9.14285714285714" style="2"/>
+    <col min="1" max="1" width="14.7181818181818" style="2" customWidth="1"/>
+    <col min="2" max="2" width="33.5727272727273" style="2" customWidth="1"/>
+    <col min="3" max="3" width="49.6636363636364" style="2" customWidth="1"/>
+    <col min="4" max="4" width="56.5545454545455" style="2" customWidth="1"/>
+    <col min="5" max="5" width="53.2818181818182" style="2" customWidth="1"/>
+    <col min="6" max="6" width="47.5727272727273" style="2" customWidth="1"/>
+    <col min="7" max="16384" width="9.14545454545454" style="2"/>
   </cols>
   <sheetData>
     <row r="1" s="1" customFormat="1" spans="1:6">
@@ -6670,7 +6749,7 @@
       <c r="E2" s="4"/>
       <c r="F2" s="4"/>
     </row>
-    <row r="3" s="2" customFormat="1" spans="1:3">
+    <row r="3" s="2" customFormat="1" spans="1:6">
       <c r="A3" s="1"/>
       <c r="B3" s="5" t="s">
         <v>19</v>
@@ -6679,7 +6758,7 @@
         <v>335</v>
       </c>
     </row>
-    <row r="4" s="2" customFormat="1" spans="1:4">
+    <row r="4" s="2" customFormat="1" spans="1:6">
       <c r="A4" s="1"/>
       <c r="B4" s="6" t="s">
         <v>21</v>
@@ -6703,7 +6782,7 @@
       <c r="E5" s="5"/>
       <c r="F5" s="5"/>
     </row>
-    <row r="6" s="2" customFormat="1" ht="30" spans="2:6">
+    <row r="6" s="2" customFormat="1" ht="29" spans="1:6">
       <c r="B6" s="7" t="s">
         <v>27</v>
       </c>
@@ -6714,7 +6793,7 @@
       <c r="E6" s="5"/>
       <c r="F6" s="5"/>
     </row>
-    <row r="7" s="2" customFormat="1" spans="2:6">
+    <row r="7" s="2" customFormat="1" spans="1:6">
       <c r="B7" s="2" t="s">
         <v>51</v>
       </c>
@@ -6729,7 +6808,7 @@
         <v>420</v>
       </c>
     </row>
-    <row r="8" s="2" customFormat="1" ht="74.25" spans="2:5">
+    <row r="8" s="2" customFormat="1" ht="71.5" spans="1:6">
       <c r="B8" s="6" t="s">
         <v>184</v>
       </c>
@@ -6743,7 +6822,7 @@
         <v>422</v>
       </c>
     </row>
-    <row r="9" s="2" customFormat="1" ht="409" customHeight="1" spans="2:5">
+    <row r="9" s="2" customFormat="1" ht="409" customHeight="1" spans="1:6">
       <c r="B9" s="6" t="s">
         <v>342</v>
       </c>
@@ -6755,7 +6834,7 @@
         <v>424</v>
       </c>
     </row>
-    <row r="10" s="2" customFormat="1" ht="150" spans="2:5">
+    <row r="10" s="2" customFormat="1" ht="145" spans="1:6">
       <c r="B10" s="6" t="s">
         <v>351</v>
       </c>
@@ -6769,7 +6848,7 @@
         <v>427</v>
       </c>
     </row>
-    <row r="11" s="2" customFormat="1" ht="180" spans="2:5">
+    <row r="11" s="2" customFormat="1" ht="159.5" spans="1:6">
       <c r="B11" s="6" t="s">
         <v>354</v>
       </c>
@@ -6779,7 +6858,7 @@
         <v>428</v>
       </c>
     </row>
-    <row r="12" s="2" customFormat="1" ht="150" spans="2:5">
+    <row r="12" s="2" customFormat="1" ht="145" spans="1:6">
       <c r="B12" s="6" t="s">
         <v>356</v>
       </c>
@@ -6789,7 +6868,7 @@
         <v>429</v>
       </c>
     </row>
-    <row r="13" s="2" customFormat="1" ht="75" spans="2:4">
+    <row r="13" s="2" customFormat="1" ht="58" spans="1:6">
       <c r="B13" s="6" t="s">
         <v>251</v>
       </c>
@@ -6800,7 +6879,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="14" s="2" customFormat="1" ht="30" spans="2:3">
+    <row r="14" s="2" customFormat="1" ht="29" spans="1:6">
       <c r="B14" s="6" t="s">
         <v>254</v>
       </c>
@@ -6808,7 +6887,7 @@
         <v>255</v>
       </c>
     </row>
-    <row r="15" s="2" customFormat="1" ht="45" spans="2:4">
+    <row r="15" s="2" customFormat="1" ht="43.5" spans="1:6">
       <c r="B15" s="6" t="s">
         <v>367</v>
       </c>
@@ -6819,7 +6898,7 @@
         <v>431</v>
       </c>
     </row>
-    <row r="16" s="2" customFormat="1" ht="30" spans="2:5">
+    <row r="16" s="2" customFormat="1" ht="29" spans="1:6">
       <c r="B16" s="6" t="s">
         <v>370</v>
       </c>
@@ -6833,7 +6912,7 @@
         <v>373</v>
       </c>
     </row>
-    <row r="17" s="2" customFormat="1" ht="45" spans="2:4">
+    <row r="17" s="2" customFormat="1" ht="43.5" spans="2:6">
       <c r="B17" s="6" t="s">
         <v>432</v>
       </c>
@@ -6857,7 +6936,7 @@
         <v>434</v>
       </c>
     </row>
-    <row r="19" s="2" customFormat="1" ht="165" spans="2:5">
+    <row r="19" s="2" customFormat="1" ht="159.5" spans="2:6">
       <c r="B19" s="2" t="s">
         <v>435</v>
       </c>
@@ -6868,7 +6947,7 @@
         <v>437</v>
       </c>
     </row>
-    <row r="20" s="2" customFormat="1" spans="2:4">
+    <row r="20" s="2" customFormat="1" spans="2:6">
       <c r="B20" s="5" t="s">
         <v>175</v>
       </c>
@@ -6879,7 +6958,7 @@
         <v>438</v>
       </c>
     </row>
-    <row r="21" s="2" customFormat="1" ht="46" customHeight="1" spans="2:4">
+    <row r="21" s="2" customFormat="1" ht="46" customHeight="1" spans="2:6">
       <c r="B21" s="5" t="s">
         <v>178</v>
       </c>
@@ -6902,118 +6981,121 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:G23"/>
-  <sheetFormatPr defaultColWidth="9.14285714285714" defaultRowHeight="15" outlineLevelCol="6"/>
+  <sheetFormatPr defaultColWidth="9.14545454545454" defaultRowHeight="14.5" outlineLevelCol="6"/>
   <cols>
-    <col min="1" max="1" width="14.7142857142857" style="64" customWidth="1"/>
-    <col min="2" max="2" width="28.2857142857143" style="64" customWidth="1"/>
-    <col min="3" max="3" width="62.7238095238095" style="64" customWidth="1"/>
-    <col min="4" max="4" width="54.5428571428571" style="64" customWidth="1"/>
+    <col min="1" max="1" width="14.7181818181818" style="65" customWidth="1"/>
+    <col min="2" max="2" width="28.2818181818182" style="65" customWidth="1"/>
+    <col min="3" max="3" width="62.7272727272727" style="65" customWidth="1"/>
+    <col min="4" max="4" width="54.5454545454545" style="65" customWidth="1"/>
     <col min="5" max="5" width="57" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
-      <c r="A1" s="65" t="s">
+      <c r="A1" s="66" t="s">
         <v>13</v>
       </c>
-      <c r="B1" s="65" t="s">
+      <c r="B1" s="66" t="s">
         <v>14</v>
       </c>
-      <c r="C1" s="65" t="s">
+      <c r="C1" s="66" t="s">
         <v>15</v>
       </c>
-      <c r="D1" s="65" t="s">
+      <c r="D1" s="66" t="s">
         <v>16</v>
       </c>
       <c r="E1" s="3" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="2" spans="1:1">
-      <c r="A2" s="66" t="s">
+    <row r="2" spans="1:5">
+      <c r="A2" s="67" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="3" spans="1:3">
-      <c r="A3" s="66"/>
-      <c r="B3" s="64" t="s">
+    <row r="3" spans="1:5">
+      <c r="A3" s="67"/>
+      <c r="B3" s="65" t="s">
         <v>19</v>
       </c>
-      <c r="C3" s="64" t="s">
+      <c r="C3" s="65" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="4" spans="1:4">
-      <c r="A4" s="66"/>
-      <c r="B4" s="64" t="s">
+    <row r="4" spans="1:5">
+      <c r="A4" s="67"/>
+      <c r="B4" s="65" t="s">
         <v>21</v>
       </c>
-      <c r="C4" s="64" t="s">
+      <c r="C4" s="65" t="s">
         <v>22</v>
       </c>
-      <c r="D4" s="64" t="s">
+      <c r="D4" s="65" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="5" ht="61" customHeight="1" spans="2:4">
-      <c r="B5" s="64" t="s">
+    <row r="5" s="64" customFormat="1" ht="61" customHeight="1" spans="1:5">
+      <c r="A5" s="68"/>
+      <c r="B5" s="68" t="s">
         <v>24</v>
       </c>
-      <c r="C5" s="64" t="s">
+      <c r="C5" s="68" t="s">
         <v>25</v>
       </c>
-      <c r="D5" s="67" t="s">
+      <c r="D5" s="69" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="6" ht="49" customHeight="1" spans="2:4">
-      <c r="B6" s="64" t="s">
+    <row r="6" s="64" customFormat="1" ht="49" customHeight="1" spans="1:5">
+      <c r="A6" s="68"/>
+      <c r="B6" s="68" t="s">
         <v>27</v>
       </c>
-      <c r="C6" s="67" t="s">
+      <c r="C6" s="68" t="s">
         <v>28</v>
       </c>
-      <c r="D6" s="67"/>
-    </row>
-    <row r="7" ht="71" customHeight="1" spans="2:4">
-      <c r="B7" s="64" t="s">
+      <c r="D6" s="69"/>
+    </row>
+    <row r="7" s="64" customFormat="1" ht="316" customHeight="1" spans="1:5">
+      <c r="A7" s="68"/>
+      <c r="B7" s="68" t="s">
         <v>29</v>
       </c>
-      <c r="C7" s="49" t="s">
+      <c r="C7" s="70" t="s">
         <v>30</v>
       </c>
-      <c r="D7" s="67"/>
-    </row>
-    <row r="8" spans="2:4">
-      <c r="B8" s="64" t="s">
+      <c r="D7" s="69"/>
+    </row>
+    <row r="8" spans="1:5">
+      <c r="B8" s="65" t="s">
         <v>31</v>
       </c>
-      <c r="C8" s="64" t="s">
+      <c r="C8" s="65" t="s">
         <v>32</v>
       </c>
-      <c r="D8" s="67"/>
-    </row>
-    <row r="9" spans="2:3">
-      <c r="B9" s="64" t="s">
+      <c r="D8" s="71"/>
+    </row>
+    <row r="9" spans="1:5">
+      <c r="B9" s="65" t="s">
         <v>33</v>
       </c>
-      <c r="C9" s="64" t="s">
+      <c r="C9" s="65" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="10" ht="30" spans="2:3">
-      <c r="B10" s="64" t="s">
+    <row r="10" ht="29" spans="1:5">
+      <c r="B10" s="65" t="s">
         <v>35</v>
       </c>
-      <c r="C10" s="67" t="s">
+      <c r="C10" s="71" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="13" s="2" customFormat="1" spans="1:1">
+    <row r="13" s="2" customFormat="1" spans="1:5">
       <c r="A13" s="3" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="14" s="2" customFormat="1" spans="2:3">
+    <row r="14" s="2" customFormat="1" spans="1:5">
       <c r="B14" s="2" t="s">
         <v>1</v>
       </c>
@@ -7021,7 +7103,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="15" s="2" customFormat="1" spans="2:3">
+    <row r="15" s="2" customFormat="1" spans="1:5">
       <c r="B15" s="2" t="s">
         <v>3</v>
       </c>
@@ -7029,7 +7111,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="16" s="2" customFormat="1" spans="2:3">
+    <row r="16" s="2" customFormat="1" spans="1:5">
       <c r="B16" s="2" t="s">
         <v>5</v>
       </c>
@@ -7037,7 +7119,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="17" s="2" customFormat="1" ht="129" customHeight="1" spans="2:7">
+    <row r="17" s="2" customFormat="1" ht="129" customHeight="1" spans="1:7">
       <c r="B17" s="2" t="s">
         <v>7</v>
       </c>
@@ -7050,7 +7132,7 @@
       <c r="F17" s="46"/>
       <c r="G17" s="46"/>
     </row>
-    <row r="18" s="2" customFormat="1" ht="30" spans="2:5">
+    <row r="18" s="2" customFormat="1" spans="1:7">
       <c r="B18" s="5" t="s">
         <v>9</v>
       </c>
@@ -7059,7 +7141,7 @@
       </c>
       <c r="E18" s="5"/>
     </row>
-    <row r="19" s="2" customFormat="1" spans="2:5">
+    <row r="19" s="2" customFormat="1" spans="1:7">
       <c r="B19" s="2" t="s">
         <v>11</v>
       </c>
@@ -7068,28 +7150,28 @@
       </c>
       <c r="E19" s="5"/>
     </row>
-    <row r="20" s="2" customFormat="1" ht="30" spans="2:5">
+    <row r="20" s="2" customFormat="1" ht="29" spans="1:7">
       <c r="B20" s="5" t="s">
         <v>44</v>
       </c>
       <c r="C20" s="2"/>
       <c r="E20" s="8"/>
     </row>
-    <row r="21" spans="1:3">
+    <row r="21" spans="1:7">
       <c r="A21"/>
       <c r="B21"/>
       <c r="C21"/>
     </row>
-    <row r="22" spans="1:3">
+    <row r="22" spans="1:7">
       <c r="A22"/>
       <c r="B22"/>
       <c r="C22"/>
     </row>
-    <row r="23" hidden="1" spans="2:3">
-      <c r="B23" s="64" t="s">
+    <row r="23" hidden="1" spans="1:7">
+      <c r="B23" s="65" t="s">
         <v>45</v>
       </c>
-      <c r="C23" s="67" t="s">
+      <c r="C23" s="71" t="s">
         <v>46</v>
       </c>
     </row>
@@ -7109,14 +7191,14 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:E65"/>
-  <sheetFormatPr defaultColWidth="9.14285714285714" defaultRowHeight="15" outlineLevelCol="4"/>
+  <sheetFormatPr defaultColWidth="9.14545454545454" defaultRowHeight="14.5" outlineLevelCol="4"/>
   <cols>
-    <col min="1" max="1" width="13.1142857142857" customWidth="1"/>
-    <col min="2" max="2" width="39.1428571428571" style="13" customWidth="1"/>
-    <col min="3" max="3" width="61.5714285714286" style="13" customWidth="1"/>
-    <col min="4" max="4" width="66.8571428571429" style="13" customWidth="1"/>
-    <col min="5" max="5" width="64.5714285714286" style="13" customWidth="1"/>
-    <col min="6" max="256" width="11.8571428571429" customWidth="1"/>
+    <col min="1" max="1" width="13.1181818181818" customWidth="1"/>
+    <col min="2" max="2" width="39.1454545454545" style="13" customWidth="1"/>
+    <col min="3" max="3" width="61.5727272727273" style="13" customWidth="1"/>
+    <col min="4" max="4" width="66.8545454545455" style="13" customWidth="1"/>
+    <col min="5" max="5" width="64.5727272727273" style="13" customWidth="1"/>
+    <col min="6" max="256" width="11.8545454545455" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" s="19" customFormat="1" spans="1:5">
@@ -7152,7 +7234,7 @@
       </c>
       <c r="E3" s="25"/>
     </row>
-    <row r="4" spans="2:5">
+    <row r="4" spans="1:5">
       <c r="B4" s="21" t="s">
         <v>21</v>
       </c>
@@ -7174,7 +7256,7 @@
       </c>
       <c r="E5" s="25"/>
     </row>
-    <row r="6" ht="30" spans="2:5">
+    <row r="6" spans="1:5">
       <c r="B6" s="21" t="s">
         <v>27</v>
       </c>
@@ -7183,7 +7265,7 @@
       </c>
       <c r="E6" s="25"/>
     </row>
-    <row r="7" ht="60" spans="2:5">
+    <row r="7" ht="58" spans="1:5">
       <c r="B7" s="13" t="s">
         <v>51</v>
       </c>
@@ -7197,7 +7279,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="8" ht="60" spans="2:5">
+    <row r="8" ht="58" spans="1:5">
       <c r="B8" s="13" t="s">
         <v>55</v>
       </c>
@@ -7209,7 +7291,7 @@
       </c>
       <c r="E8" s="25"/>
     </row>
-    <row r="9" spans="2:5">
+    <row r="9" spans="1:5">
       <c r="B9" s="13" t="s">
         <v>58</v>
       </c>
@@ -7218,7 +7300,7 @@
       </c>
       <c r="E9" s="25"/>
     </row>
-    <row r="10" spans="2:5">
+    <row r="10" spans="1:5">
       <c r="B10" s="13" t="s">
         <v>60</v>
       </c>
@@ -7230,7 +7312,7 @@
       </c>
       <c r="E10" s="25"/>
     </row>
-    <row r="11" spans="2:5">
+    <row r="11" spans="1:5">
       <c r="B11" s="21" t="s">
         <v>63</v>
       </c>
@@ -7242,7 +7324,7 @@
       </c>
       <c r="E11" s="25"/>
     </row>
-    <row r="12" spans="2:5">
+    <row r="12" spans="1:5">
       <c r="B12" s="21" t="s">
         <v>66</v>
       </c>
@@ -7254,7 +7336,7 @@
       </c>
       <c r="E12" s="25"/>
     </row>
-    <row r="13" ht="60" spans="2:5">
+    <row r="13" ht="58" spans="1:5">
       <c r="B13" s="13" t="s">
         <v>68</v>
       </c>
@@ -7266,7 +7348,7 @@
       </c>
       <c r="E13" s="25"/>
     </row>
-    <row r="14" ht="30" spans="2:5">
+    <row r="14" ht="29" spans="1:5">
       <c r="B14" s="13" t="s">
         <v>71</v>
       </c>
@@ -7278,7 +7360,7 @@
       </c>
       <c r="E14" s="25"/>
     </row>
-    <row r="15" spans="2:5">
+    <row r="15" spans="1:5">
       <c r="B15" s="21" t="s">
         <v>74</v>
       </c>
@@ -7290,7 +7372,7 @@
       </c>
       <c r="E15" s="25"/>
     </row>
-    <row r="16" spans="2:5">
+    <row r="16" spans="1:5">
       <c r="B16" s="21" t="s">
         <v>77</v>
       </c>
@@ -7302,7 +7384,7 @@
       </c>
       <c r="E16" s="25"/>
     </row>
-    <row r="17" ht="135" spans="2:5">
+    <row r="17" ht="130.5" spans="2:5">
       <c r="B17" s="13" t="s">
         <v>80</v>
       </c>
@@ -7359,7 +7441,7 @@
       </c>
       <c r="E22" s="25"/>
     </row>
-    <row r="23" ht="90" spans="2:5">
+    <row r="23" ht="87" spans="2:5">
       <c r="B23" s="13" t="s">
         <v>93</v>
       </c>
@@ -7370,7 +7452,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="24" ht="75" spans="2:5">
+    <row r="24" ht="72.5" spans="2:5">
       <c r="B24" s="13" t="s">
         <v>96</v>
       </c>
@@ -7393,7 +7475,7 @@
       </c>
       <c r="E25" s="25"/>
     </row>
-    <row r="26" ht="30" spans="2:5">
+    <row r="26" ht="29" spans="2:5">
       <c r="B26" s="13" t="s">
         <v>102</v>
       </c>
@@ -7402,7 +7484,7 @@
       </c>
       <c r="E26" s="48"/>
     </row>
-    <row r="27" ht="45" spans="2:5">
+    <row r="27" ht="29" spans="2:5">
       <c r="B27" s="29" t="s">
         <v>104</v>
       </c>
@@ -7416,7 +7498,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="28" ht="30" spans="2:5">
+    <row r="28" ht="29" spans="2:5">
       <c r="B28" s="29" t="s">
         <v>108</v>
       </c>
@@ -7426,7 +7508,7 @@
       <c r="D28" s="60"/>
       <c r="E28" s="61"/>
     </row>
-    <row r="29" ht="30" spans="2:5">
+    <row r="29" spans="2:5">
       <c r="B29" s="29" t="s">
         <v>110</v>
       </c>
@@ -7436,7 +7518,7 @@
       <c r="D29" s="60"/>
       <c r="E29" s="61"/>
     </row>
-    <row r="30" ht="30" spans="2:5">
+    <row r="30" ht="29" spans="2:5">
       <c r="B30" s="29" t="s">
         <v>112</v>
       </c>
@@ -7456,7 +7538,7 @@
       <c r="D31" s="60"/>
       <c r="E31" s="8"/>
     </row>
-    <row r="32" ht="30" spans="2:5">
+    <row r="32" ht="29" spans="2:5">
       <c r="B32" s="29" t="s">
         <v>104</v>
       </c>
@@ -7470,7 +7552,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="33" ht="30" spans="2:5">
+    <row r="33" ht="29" spans="2:5">
       <c r="B33" s="29" t="s">
         <v>108</v>
       </c>
@@ -7480,7 +7562,7 @@
       <c r="D33" s="60"/>
       <c r="E33" s="61"/>
     </row>
-    <row r="34" ht="30" spans="2:5">
+    <row r="34" spans="2:5">
       <c r="B34" s="29" t="s">
         <v>110</v>
       </c>
@@ -7490,7 +7572,7 @@
       <c r="D34" s="60"/>
       <c r="E34" s="61"/>
     </row>
-    <row r="35" ht="30" spans="2:5">
+    <row r="35" ht="29" spans="2:5">
       <c r="B35" s="29" t="s">
         <v>112</v>
       </c>
@@ -7522,7 +7604,7 @@
       </c>
       <c r="E37" s="61"/>
     </row>
-    <row r="38" ht="45" spans="2:5">
+    <row r="38" ht="43.5" spans="2:5">
       <c r="B38" s="29" t="s">
         <v>123</v>
       </c>
@@ -7530,11 +7612,11 @@
         <v>124</v>
       </c>
       <c r="D38" s="60"/>
-      <c r="E38" s="69" t="s">
+      <c r="E38" s="73" t="s">
         <v>125</v>
       </c>
     </row>
-    <row r="39" ht="135" spans="2:5">
+    <row r="39" ht="130.5" spans="2:5">
       <c r="B39" s="62" t="s">
         <v>126</v>
       </c>
@@ -7546,7 +7628,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="40" ht="135" spans="2:5">
+    <row r="40" ht="130.5" spans="2:5">
       <c r="B40" s="62" t="s">
         <v>129</v>
       </c>
@@ -7594,7 +7676,7 @@
       </c>
       <c r="E44" s="25"/>
     </row>
-    <row r="45" ht="195" spans="2:5">
+    <row r="45" ht="188.5" spans="2:5">
       <c r="B45" s="21" t="s">
         <v>138</v>
       </c>
@@ -7606,7 +7688,7 @@
       </c>
       <c r="E45" s="25"/>
     </row>
-    <row r="46" ht="195" spans="2:5">
+    <row r="46" ht="188.5" spans="2:5">
       <c r="B46" s="21" t="s">
         <v>141</v>
       </c>
@@ -7620,7 +7702,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="47" ht="195" spans="2:5">
+    <row r="47" ht="188.5" spans="2:5">
       <c r="B47" s="21" t="s">
         <v>145</v>
       </c>
@@ -7668,7 +7750,7 @@
       </c>
       <c r="E51" s="25"/>
     </row>
-    <row r="52" ht="150" spans="2:5">
+    <row r="52" ht="145" spans="2:5">
       <c r="B52" s="13" t="s">
         <v>154</v>
       </c>
@@ -7736,7 +7818,7 @@
       </c>
       <c r="E58" s="25"/>
     </row>
-    <row r="59" ht="180" spans="2:5">
+    <row r="59" ht="174" spans="2:5">
       <c r="B59" s="13" t="s">
         <v>168</v>
       </c>
@@ -7748,7 +7830,7 @@
       </c>
       <c r="E59" s="25"/>
     </row>
-    <row r="60" ht="255" spans="2:5">
+    <row r="60" ht="246.5" spans="2:5">
       <c r="B60" s="13" t="s">
         <v>171</v>
       </c>
@@ -7809,14 +7891,14 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:E22"/>
-  <sheetFormatPr defaultColWidth="9.14285714285714" defaultRowHeight="15" outlineLevelCol="4"/>
+  <sheetFormatPr defaultColWidth="9.14545454545454" defaultRowHeight="14.5" outlineLevelCol="4"/>
   <cols>
-    <col min="1" max="1" width="9.14285714285714" customWidth="1"/>
-    <col min="2" max="2" width="40.8571428571429" customWidth="1"/>
-    <col min="3" max="3" width="61.5714285714286" customWidth="1"/>
-    <col min="4" max="4" width="57.4285714285714" customWidth="1"/>
-    <col min="5" max="5" width="54.8571428571429" customWidth="1"/>
-    <col min="6" max="6" width="9.14285714285714" customWidth="1"/>
+    <col min="1" max="1" width="9.14545454545454" customWidth="1"/>
+    <col min="2" max="2" width="40.8545454545455" customWidth="1"/>
+    <col min="3" max="3" width="61.5727272727273" customWidth="1"/>
+    <col min="4" max="4" width="57.4272727272727" customWidth="1"/>
+    <col min="5" max="5" width="54.8545454545455" customWidth="1"/>
+    <col min="6" max="6" width="9.14545454545454" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
@@ -7847,7 +7929,7 @@
       <c r="D2" s="53"/>
       <c r="E2" s="53"/>
     </row>
-    <row r="3" spans="2:5">
+    <row r="3" spans="1:5">
       <c r="B3" s="13" t="s">
         <v>19</v>
       </c>
@@ -7856,7 +7938,7 @@
       </c>
       <c r="E3" s="25"/>
     </row>
-    <row r="4" spans="2:5">
+    <row r="4" spans="1:5">
       <c r="B4" s="20" t="s">
         <v>21</v>
       </c>
@@ -7865,7 +7947,7 @@
       </c>
       <c r="E4" s="25"/>
     </row>
-    <row r="5" spans="2:5">
+    <row r="5" spans="1:5">
       <c r="B5" s="20" t="s">
         <v>24</v>
       </c>
@@ -7874,7 +7956,7 @@
       </c>
       <c r="E5" s="25"/>
     </row>
-    <row r="6" spans="2:5">
+    <row r="6" spans="1:5">
       <c r="B6" s="20" t="s">
         <v>27</v>
       </c>
@@ -7883,7 +7965,7 @@
       </c>
       <c r="E6" s="25"/>
     </row>
-    <row r="7" ht="45" spans="2:5">
+    <row r="7" ht="29" spans="1:5">
       <c r="B7" s="20" t="s">
         <v>184</v>
       </c>
@@ -7897,7 +7979,7 @@
         <v>187</v>
       </c>
     </row>
-    <row r="8" ht="135" spans="2:5">
+    <row r="8" ht="130.5" spans="1:5">
       <c r="B8" s="55" t="s">
         <v>188</v>
       </c>
@@ -7911,7 +7993,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="9" spans="2:5">
+    <row r="9" spans="1:5">
       <c r="B9" s="55" t="s">
         <v>192</v>
       </c>
@@ -7921,7 +8003,7 @@
       <c r="D9" s="28"/>
       <c r="E9" s="25"/>
     </row>
-    <row r="10" spans="2:5">
+    <row r="10" spans="1:5">
       <c r="B10" s="55" t="s">
         <v>194</v>
       </c>
@@ -7933,7 +8015,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="11" ht="225" spans="2:5">
+    <row r="11" ht="217.5" spans="1:5">
       <c r="B11" s="20" t="s">
         <v>197</v>
       </c>
@@ -7947,7 +8029,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="12" spans="2:5">
+    <row r="12" spans="1:5">
       <c r="B12" s="20" t="s">
         <v>200</v>
       </c>
@@ -7958,7 +8040,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="13" spans="2:5">
+    <row r="13" spans="1:5">
       <c r="B13" s="20" t="s">
         <v>202</v>
       </c>
@@ -7969,7 +8051,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="14" ht="30" spans="2:5">
+    <row r="14" ht="29" spans="1:5">
       <c r="B14" s="20" t="s">
         <v>204</v>
       </c>
@@ -7983,7 +8065,7 @@
         <v>207</v>
       </c>
     </row>
-    <row r="15" ht="135" spans="2:5">
+    <row r="15" ht="116" spans="1:5">
       <c r="B15" s="20" t="s">
         <v>208</v>
       </c>
@@ -7997,7 +8079,7 @@
         <v>211</v>
       </c>
     </row>
-    <row r="16" ht="45" spans="2:5">
+    <row r="16" ht="43.5" spans="1:5">
       <c r="B16" s="20" t="s">
         <v>212</v>
       </c>
@@ -8009,7 +8091,7 @@
       </c>
       <c r="E16" s="25"/>
     </row>
-    <row r="17" ht="60" spans="2:5">
+    <row r="17" ht="58" spans="2:5">
       <c r="B17" s="55" t="s">
         <v>215</v>
       </c>
@@ -8021,7 +8103,7 @@
       </c>
       <c r="E17" s="25"/>
     </row>
-    <row r="18" ht="60" spans="2:5">
+    <row r="18" ht="58" spans="2:5">
       <c r="B18" s="58" t="s">
         <v>218</v>
       </c>
@@ -8098,14 +8180,14 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:E29"/>
-  <sheetFormatPr defaultColWidth="9.14285714285714" defaultRowHeight="15" outlineLevelCol="4"/>
+  <sheetFormatPr defaultColWidth="9.14545454545454" defaultRowHeight="14.5" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
     <col min="2" max="2" width="46" customWidth="1"/>
     <col min="3" max="3" width="50" customWidth="1"/>
-    <col min="4" max="4" width="43.5714285714286" customWidth="1"/>
-    <col min="5" max="5" width="57.5714285714286" customWidth="1"/>
-    <col min="6" max="6" width="9.14285714285714" customWidth="1"/>
+    <col min="4" max="4" width="43.5727272727273" customWidth="1"/>
+    <col min="5" max="5" width="57.5727272727273" customWidth="1"/>
+    <col min="6" max="6" width="9.14545454545454" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
@@ -8131,7 +8213,7 @@
       </c>
       <c r="E2" s="25"/>
     </row>
-    <row r="3" spans="2:5">
+    <row r="3" spans="1:5">
       <c r="B3" s="13" t="s">
         <v>19</v>
       </c>
@@ -8164,7 +8246,7 @@
       <c r="D5" s="13"/>
       <c r="E5" s="25"/>
     </row>
-    <row r="6" ht="30" spans="2:5">
+    <row r="6" ht="29" spans="1:5">
       <c r="B6" s="21" t="s">
         <v>27</v>
       </c>
@@ -8174,7 +8256,7 @@
       <c r="D6" s="13"/>
       <c r="E6" s="25"/>
     </row>
-    <row r="7" spans="2:5">
+    <row r="7" spans="1:5">
       <c r="B7" s="20" t="s">
         <v>184</v>
       </c>
@@ -8186,7 +8268,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="8" ht="75" spans="2:5">
+    <row r="8" ht="72.5" spans="1:5">
       <c r="B8" s="20" t="s">
         <v>232</v>
       </c>
@@ -8196,11 +8278,11 @@
       <c r="D8" s="13" t="s">
         <v>234</v>
       </c>
-      <c r="E8" s="70" t="s">
+      <c r="E8" s="74" t="s">
         <v>235</v>
       </c>
     </row>
-    <row r="9" spans="2:5">
+    <row r="9" spans="1:5">
       <c r="B9" s="20" t="s">
         <v>236</v>
       </c>
@@ -8210,7 +8292,7 @@
       <c r="D9" s="13"/>
       <c r="E9" s="25"/>
     </row>
-    <row r="10" ht="75" spans="2:5">
+    <row r="10" ht="72.5" spans="1:5">
       <c r="B10" s="20" t="s">
         <v>238</v>
       </c>
@@ -8218,11 +8300,11 @@
         <v>239</v>
       </c>
       <c r="D10" s="13"/>
-      <c r="E10" s="70" t="s">
+      <c r="E10" s="74" t="s">
         <v>240</v>
       </c>
     </row>
-    <row r="11" ht="120" spans="2:5">
+    <row r="11" ht="116" spans="1:5">
       <c r="B11" s="20" t="s">
         <v>241</v>
       </c>
@@ -8236,7 +8318,7 @@
         <v>244</v>
       </c>
     </row>
-    <row r="12" ht="60" spans="2:5">
+    <row r="12" ht="43.5" spans="1:5">
       <c r="B12" s="20" t="s">
         <v>245</v>
       </c>
@@ -8244,7 +8326,7 @@
         <v>246</v>
       </c>
     </row>
-    <row r="13" spans="2:5">
+    <row r="13" spans="1:5">
       <c r="B13" s="20" t="s">
         <v>247</v>
       </c>
@@ -8253,7 +8335,7 @@
       </c>
       <c r="E13" s="25"/>
     </row>
-    <row r="14" spans="2:5">
+    <row r="14" spans="1:5">
       <c r="B14" t="s">
         <v>249</v>
       </c>
@@ -8262,7 +8344,7 @@
       </c>
       <c r="E14" s="25"/>
     </row>
-    <row r="15" ht="75" spans="2:5">
+    <row r="15" ht="72.5" spans="1:5">
       <c r="B15" s="20" t="s">
         <v>251</v>
       </c>
@@ -8274,7 +8356,7 @@
       </c>
       <c r="E15" s="25"/>
     </row>
-    <row r="16" ht="30" spans="2:5">
+    <row r="16" ht="29" spans="1:5">
       <c r="B16" s="20" t="s">
         <v>254</v>
       </c>
@@ -8283,7 +8365,7 @@
       </c>
       <c r="E16" s="25"/>
     </row>
-    <row r="17" ht="60" spans="2:5">
+    <row r="17" ht="58" spans="2:5">
       <c r="B17" t="s">
         <v>256</v>
       </c>
@@ -8304,7 +8386,7 @@
       </c>
       <c r="E18" s="25"/>
     </row>
-    <row r="19" ht="30" spans="2:5">
+    <row r="19" ht="29" spans="2:5">
       <c r="B19" t="s">
         <v>261</v>
       </c>
@@ -8352,7 +8434,7 @@
         <v>267</v>
       </c>
     </row>
-    <row r="23" ht="30" spans="2:5">
+    <row r="23" ht="29" spans="2:5">
       <c r="B23" t="s">
         <v>271</v>
       </c>
@@ -8364,7 +8446,7 @@
         <v>267</v>
       </c>
     </row>
-    <row r="24" ht="75" spans="2:5">
+    <row r="24" ht="72.5" spans="2:5">
       <c r="B24" t="s">
         <v>273</v>
       </c>
@@ -8384,7 +8466,7 @@
       <c r="D25" s="13"/>
       <c r="E25" s="25"/>
     </row>
-    <row r="26" ht="60" spans="2:5">
+    <row r="26" ht="58" spans="2:5">
       <c r="B26" t="s">
         <v>277</v>
       </c>
@@ -8410,7 +8492,7 @@
         <v>280</v>
       </c>
     </row>
-    <row r="28" customHeight="1" spans="2:5">
+    <row r="28" ht="15" customHeight="1" spans="2:5">
       <c r="B28" s="13" t="s">
         <v>175</v>
       </c>
@@ -8422,7 +8504,7 @@
       </c>
       <c r="E28" s="25"/>
     </row>
-    <row r="29" ht="30" spans="2:5">
+    <row r="29" ht="29" spans="2:5">
       <c r="B29" s="13" t="s">
         <v>178</v>
       </c>
@@ -8447,15 +8529,15 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:F31"/>
-  <sheetFormatPr defaultColWidth="9.14285714285714" defaultRowHeight="15" outlineLevelCol="5"/>
+  <sheetFormatPr defaultColWidth="9.14545454545454" defaultRowHeight="14.5" outlineLevelCol="5"/>
   <cols>
-    <col min="1" max="1" width="19.4285714285714" style="31" customWidth="1"/>
+    <col min="1" max="1" width="19.4272727272727" style="31" customWidth="1"/>
     <col min="2" max="2" width="37" style="31" customWidth="1"/>
-    <col min="3" max="3" width="50.5714285714286" style="31" customWidth="1"/>
-    <col min="4" max="4" width="39.1428571428571" style="31" customWidth="1"/>
-    <col min="5" max="5" width="54.1428571428571" style="31" customWidth="1"/>
-    <col min="6" max="6" width="51.1428571428571" style="31" customWidth="1"/>
-    <col min="7" max="16384" width="9.14285714285714" style="31"/>
+    <col min="3" max="3" width="50.5727272727273" style="31" customWidth="1"/>
+    <col min="4" max="4" width="39.1454545454545" style="31" customWidth="1"/>
+    <col min="5" max="5" width="54.1454545454545" style="31" customWidth="1"/>
+    <col min="6" max="6" width="51.1454545454545" style="31" customWidth="1"/>
+    <col min="7" max="16384" width="9.14545454545454" style="31"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6">
@@ -8478,13 +8560,13 @@
         <v>285</v>
       </c>
     </row>
-    <row r="2" spans="1:5">
+    <row r="2" spans="1:6">
       <c r="A2" s="33" t="s">
         <v>5</v>
       </c>
       <c r="E2" s="34"/>
     </row>
-    <row r="3" spans="2:5">
+    <row r="3" spans="1:6">
       <c r="B3" s="35" t="s">
         <v>19</v>
       </c>
@@ -8493,7 +8575,7 @@
       </c>
       <c r="E3" s="34"/>
     </row>
-    <row r="4" spans="2:5">
+    <row r="4" spans="1:6">
       <c r="B4" s="31" t="s">
         <v>21</v>
       </c>
@@ -8502,7 +8584,7 @@
       </c>
       <c r="E4" s="34"/>
     </row>
-    <row r="5" spans="1:5">
+    <row r="5" spans="1:6">
       <c r="A5" s="33"/>
       <c r="B5" s="35" t="s">
         <v>24</v>
@@ -8513,7 +8595,7 @@
       <c r="D5" s="35"/>
       <c r="E5" s="34"/>
     </row>
-    <row r="6" ht="30" spans="2:5">
+    <row r="6" ht="29" spans="1:6">
       <c r="B6" s="35" t="s">
         <v>27</v>
       </c>
@@ -8523,7 +8605,7 @@
       <c r="D6" s="35"/>
       <c r="E6" s="34"/>
     </row>
-    <row r="7" ht="30" spans="2:6">
+    <row r="7" ht="29" spans="1:6">
       <c r="B7" s="36" t="s">
         <v>288</v>
       </c>
@@ -8536,7 +8618,7 @@
       </c>
       <c r="F7" s="38"/>
     </row>
-    <row r="8" ht="195" spans="2:5">
+    <row r="8" ht="188.5" spans="1:6">
       <c r="B8" s="31" t="s">
         <v>291</v>
       </c>
@@ -8550,7 +8632,7 @@
         <v>294</v>
       </c>
     </row>
-    <row r="9" spans="2:5">
+    <row r="9" spans="1:6">
       <c r="B9" s="31" t="s">
         <v>295</v>
       </c>
@@ -8560,7 +8642,7 @@
       <c r="D9" s="35"/>
       <c r="E9" s="34"/>
     </row>
-    <row r="10" spans="2:5">
+    <row r="10" spans="1:6">
       <c r="B10" s="35" t="s">
         <v>297</v>
       </c>
@@ -8570,7 +8652,7 @@
       <c r="D10" s="35"/>
       <c r="E10" s="34"/>
     </row>
-    <row r="11" ht="30" spans="2:5">
+    <row r="11" spans="1:6">
       <c r="B11" s="35" t="s">
         <v>299</v>
       </c>
@@ -8580,7 +8662,7 @@
       <c r="D11" s="35"/>
       <c r="E11" s="34"/>
     </row>
-    <row r="12" ht="30" spans="2:5">
+    <row r="12" spans="1:6">
       <c r="B12" s="35" t="s">
         <v>300</v>
       </c>
@@ -8590,7 +8672,7 @@
       <c r="D12" s="35"/>
       <c r="E12" s="34"/>
     </row>
-    <row r="13" ht="225" spans="2:5">
+    <row r="13" ht="217.5" spans="1:6">
       <c r="B13" s="31" t="s">
         <v>302</v>
       </c>
@@ -8604,7 +8686,7 @@
         <v>305</v>
       </c>
     </row>
-    <row r="14" spans="2:5">
+    <row r="14" spans="1:6">
       <c r="B14" s="31" t="s">
         <v>306</v>
       </c>
@@ -8614,7 +8696,7 @@
       <c r="D14" s="35"/>
       <c r="E14" s="34"/>
     </row>
-    <row r="15" spans="2:5">
+    <row r="15" spans="1:6">
       <c r="B15" s="35" t="s">
         <v>308</v>
       </c>
@@ -8624,7 +8706,7 @@
       <c r="D15" s="35"/>
       <c r="E15" s="34"/>
     </row>
-    <row r="16" ht="30" spans="2:5">
+    <row r="16" spans="1:6">
       <c r="B16" s="35" t="s">
         <v>310</v>
       </c>
@@ -8634,7 +8716,7 @@
       <c r="D16" s="35"/>
       <c r="E16" s="34"/>
     </row>
-    <row r="17" ht="30" spans="2:5">
+    <row r="17" spans="2:6">
       <c r="B17" s="35" t="s">
         <v>311</v>
       </c>
@@ -8644,7 +8726,7 @@
       <c r="D17" s="35"/>
       <c r="E17" s="34"/>
     </row>
-    <row r="18" ht="30" spans="2:5">
+    <row r="18" ht="29" spans="2:6">
       <c r="B18" s="41" t="s">
         <v>313</v>
       </c>
@@ -8658,7 +8740,7 @@
         <v>316</v>
       </c>
     </row>
-    <row r="19" ht="135" spans="2:5">
+    <row r="19" ht="130.5" spans="2:6">
       <c r="B19" s="37" t="s">
         <v>317</v>
       </c>
@@ -8670,7 +8752,7 @@
         <v>319</v>
       </c>
     </row>
-    <row r="20" ht="75" spans="2:5">
+    <row r="20" ht="72.5" spans="2:6">
       <c r="B20" s="35" t="s">
         <v>96</v>
       </c>
@@ -8682,7 +8764,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="21" ht="180" spans="2:5">
+    <row r="21" ht="174" spans="2:6">
       <c r="B21" s="35" t="s">
         <v>100</v>
       </c>
@@ -8705,7 +8787,7 @@
       <c r="E22" s="48"/>
       <c r="F22" s="49"/>
     </row>
-    <row r="23" ht="30" spans="2:5">
+    <row r="23" ht="29" spans="2:6">
       <c r="B23" s="35" t="s">
         <v>80</v>
       </c>
@@ -8717,7 +8799,7 @@
       </c>
       <c r="E23" s="34"/>
     </row>
-    <row r="24" ht="90" spans="2:5">
+    <row r="24" ht="87" spans="2:6">
       <c r="B24" s="35" t="s">
         <v>93</v>
       </c>
@@ -8729,7 +8811,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="25" ht="45" spans="2:5">
+    <row r="25" ht="43.5" spans="2:6">
       <c r="B25" s="35" t="s">
         <v>83</v>
       </c>
@@ -8739,7 +8821,7 @@
       <c r="D25" s="35"/>
       <c r="E25" s="34"/>
     </row>
-    <row r="26" spans="2:5">
+    <row r="26" spans="2:6">
       <c r="B26" s="35" t="s">
         <v>85</v>
       </c>
@@ -8749,7 +8831,7 @@
       <c r="D26" s="35"/>
       <c r="E26" s="34"/>
     </row>
-    <row r="27" spans="2:5">
+    <row r="27" spans="2:6">
       <c r="B27" s="35" t="s">
         <v>87</v>
       </c>
@@ -8759,7 +8841,7 @@
       <c r="D27" s="35"/>
       <c r="E27" s="34"/>
     </row>
-    <row r="28" spans="2:5">
+    <row r="28" spans="2:6">
       <c r="B28" s="35" t="s">
         <v>89</v>
       </c>
@@ -8769,7 +8851,7 @@
       <c r="D28" s="35"/>
       <c r="E28" s="34"/>
     </row>
-    <row r="29" spans="2:5">
+    <row r="29" spans="2:6">
       <c r="B29" s="35" t="s">
         <v>91</v>
       </c>
@@ -8779,7 +8861,7 @@
       <c r="D29" s="35"/>
       <c r="E29" s="34"/>
     </row>
-    <row r="30" customHeight="1" spans="2:5">
+    <row r="30" ht="15" customHeight="1" spans="2:6">
       <c r="B30" s="35" t="s">
         <v>175</v>
       </c>
@@ -8791,7 +8873,7 @@
       </c>
       <c r="E30" s="34"/>
     </row>
-    <row r="31" ht="30" spans="2:5">
+    <row r="31" ht="29" spans="2:6">
       <c r="B31" s="35" t="s">
         <v>178</v>
       </c>
@@ -8815,14 +8897,14 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:E28"/>
-  <sheetFormatPr defaultColWidth="9.14285714285714" defaultRowHeight="15" outlineLevelCol="4"/>
+  <sheetFormatPr defaultColWidth="9.14545454545454" defaultRowHeight="14.5" outlineLevelCol="4"/>
   <cols>
-    <col min="1" max="1" width="13.2190476190476" customWidth="1"/>
-    <col min="2" max="2" width="26.2857142857143" customWidth="1"/>
-    <col min="3" max="3" width="43.7142857142857" customWidth="1"/>
-    <col min="4" max="4" width="47.2857142857143" customWidth="1"/>
-    <col min="5" max="5" width="80.5714285714286" customWidth="1"/>
-    <col min="6" max="6" width="9.14285714285714" customWidth="1"/>
+    <col min="1" max="1" width="13.2181818181818" customWidth="1"/>
+    <col min="2" max="2" width="26.2818181818182" customWidth="1"/>
+    <col min="3" max="3" width="43.7181818181818" customWidth="1"/>
+    <col min="4" max="4" width="47.2818181818182" customWidth="1"/>
+    <col min="5" max="5" width="80.5727272727273" customWidth="1"/>
+    <col min="6" max="6" width="9.14545454545454" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
@@ -8848,7 +8930,7 @@
       </c>
       <c r="E2" s="13"/>
     </row>
-    <row r="3" spans="2:5">
+    <row r="3" spans="1:5">
       <c r="B3" s="13" t="s">
         <v>19</v>
       </c>
@@ -8857,7 +8939,7 @@
       </c>
       <c r="E3" s="13"/>
     </row>
-    <row r="4" spans="2:5">
+    <row r="4" spans="1:5">
       <c r="B4" s="13" t="s">
         <v>21</v>
       </c>
@@ -8869,7 +8951,7 @@
       </c>
       <c r="E4" s="13"/>
     </row>
-    <row r="5" spans="2:5">
+    <row r="5" spans="1:5">
       <c r="B5" s="21" t="s">
         <v>24</v>
       </c>
@@ -8878,7 +8960,7 @@
       </c>
       <c r="E5" s="13"/>
     </row>
-    <row r="6" ht="30" spans="2:5">
+    <row r="6" ht="29" spans="1:5">
       <c r="B6" s="21" t="s">
         <v>27</v>
       </c>
@@ -8887,7 +8969,7 @@
       </c>
       <c r="E6" s="13"/>
     </row>
-    <row r="7" spans="2:5">
+    <row r="7" spans="1:5">
       <c r="B7" s="21" t="s">
         <v>51</v>
       </c>
@@ -8899,7 +8981,7 @@
         <v>338</v>
       </c>
     </row>
-    <row r="8" ht="74.25" spans="2:5">
+    <row r="8" ht="71.5" spans="1:5">
       <c r="B8" s="21" t="s">
         <v>184</v>
       </c>
@@ -8913,7 +8995,7 @@
         <v>341</v>
       </c>
     </row>
-    <row r="9" ht="120" spans="2:5">
+    <row r="9" ht="116" spans="1:5">
       <c r="B9" s="27" t="s">
         <v>342</v>
       </c>
@@ -8925,7 +9007,7 @@
         <v>344</v>
       </c>
     </row>
-    <row r="10" ht="45" spans="1:5">
+    <row r="10" ht="43.5" spans="1:5">
       <c r="A10" s="28"/>
       <c r="B10" s="6" t="s">
         <v>202</v>
@@ -8938,7 +9020,7 @@
         <v>346</v>
       </c>
     </row>
-    <row r="11" ht="210" spans="1:5">
+    <row r="11" ht="203" spans="1:5">
       <c r="A11" s="28"/>
       <c r="B11" s="6" t="s">
         <v>197</v>
@@ -8949,7 +9031,7 @@
         <v>347</v>
       </c>
     </row>
-    <row r="12" ht="210" spans="1:5">
+    <row r="12" ht="203" spans="1:5">
       <c r="A12" s="28"/>
       <c r="B12" s="6" t="s">
         <v>200</v>
@@ -8971,7 +9053,7 @@
         <v>350</v>
       </c>
     </row>
-    <row r="14" ht="150" spans="2:5">
+    <row r="14" ht="130.5" spans="1:5">
       <c r="B14" s="13" t="s">
         <v>351</v>
       </c>
@@ -8983,7 +9065,7 @@
       </c>
       <c r="E14" s="13"/>
     </row>
-    <row r="15" spans="2:5">
+    <row r="15" spans="1:5">
       <c r="B15" s="21" t="s">
         <v>354</v>
       </c>
@@ -8992,7 +9074,7 @@
       </c>
       <c r="E15" s="13"/>
     </row>
-    <row r="16" spans="2:5">
+    <row r="16" spans="1:5">
       <c r="B16" s="21" t="s">
         <v>356</v>
       </c>
@@ -9010,7 +9092,7 @@
       </c>
       <c r="E17" s="13"/>
     </row>
-    <row r="18" ht="105" spans="2:5">
+    <row r="18" ht="101.5" spans="2:5">
       <c r="B18" s="13" t="s">
         <v>359</v>
       </c>
@@ -9024,7 +9106,7 @@
         <v>362</v>
       </c>
     </row>
-    <row r="19" ht="30" spans="2:5">
+    <row r="19" ht="29" spans="2:5">
       <c r="B19" s="13" t="s">
         <v>363</v>
       </c>
@@ -9035,7 +9117,7 @@
         <v>362</v>
       </c>
     </row>
-    <row r="20" ht="30" spans="2:5">
+    <row r="20" ht="29" spans="2:5">
       <c r="B20" s="13" t="s">
         <v>364</v>
       </c>
@@ -9046,7 +9128,7 @@
         <v>362</v>
       </c>
     </row>
-    <row r="21" ht="75" spans="2:5">
+    <row r="21" ht="72.5" spans="2:5">
       <c r="B21" s="21" t="s">
         <v>251</v>
       </c>
@@ -9058,7 +9140,7 @@
       </c>
       <c r="E21" s="13"/>
     </row>
-    <row r="22" ht="30" spans="2:5">
+    <row r="22" ht="29" spans="2:5">
       <c r="B22" s="21" t="s">
         <v>254</v>
       </c>
@@ -9067,7 +9149,7 @@
       </c>
       <c r="E22" s="13"/>
     </row>
-    <row r="23" ht="45" spans="2:5">
+    <row r="23" ht="43.5" spans="2:5">
       <c r="B23" s="27" t="s">
         <v>367</v>
       </c>
@@ -9079,7 +9161,7 @@
       </c>
       <c r="E23" s="13"/>
     </row>
-    <row r="24" ht="30" spans="2:5">
+    <row r="24" spans="2:5">
       <c r="B24" s="21" t="s">
         <v>370</v>
       </c>
@@ -9093,7 +9175,7 @@
         <v>373</v>
       </c>
     </row>
-    <row r="25" ht="60" spans="2:5">
+    <row r="25" ht="58" spans="2:5">
       <c r="B25" s="13" t="s">
         <v>374</v>
       </c>
@@ -9105,7 +9187,7 @@
       </c>
       <c r="E25" s="13"/>
     </row>
-    <row r="26" ht="30" spans="2:5">
+    <row r="26" ht="29" spans="2:5">
       <c r="B26" s="13" t="s">
         <v>376</v>
       </c>
@@ -9160,14 +9242,14 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:E19"/>
-  <sheetFormatPr defaultColWidth="9.14285714285714" defaultRowHeight="15" outlineLevelCol="4"/>
+  <sheetFormatPr defaultColWidth="9.14545454545454" defaultRowHeight="14.5" outlineLevelCol="4"/>
   <cols>
-    <col min="1" max="1" width="22.2857142857143" customWidth="1"/>
+    <col min="1" max="1" width="22.2818181818182" customWidth="1"/>
     <col min="2" max="2" width="34" customWidth="1"/>
-    <col min="3" max="3" width="70.2857142857143" customWidth="1"/>
-    <col min="4" max="4" width="47.1428571428571" customWidth="1"/>
-    <col min="5" max="5" width="49.5714285714286" customWidth="1"/>
-    <col min="6" max="6" width="9.14285714285714" customWidth="1"/>
+    <col min="3" max="3" width="70.2818181818182" customWidth="1"/>
+    <col min="4" max="4" width="47.1454545454545" customWidth="1"/>
+    <col min="5" max="5" width="49.5727272727273" customWidth="1"/>
+    <col min="6" max="6" width="9.14545454545454" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
@@ -9187,7 +9269,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="2" ht="30" spans="1:5">
+    <row r="2" ht="29" spans="1:5">
       <c r="A2" s="24" t="s">
         <v>381</v>
       </c>
@@ -9227,7 +9309,7 @@
       <c r="D5" s="13"/>
       <c r="E5" s="25"/>
     </row>
-    <row r="6" ht="30" spans="2:5">
+    <row r="6" ht="29" spans="1:5">
       <c r="B6" s="21" t="s">
         <v>27</v>
       </c>
@@ -9237,7 +9319,7 @@
       <c r="D6" s="13"/>
       <c r="E6" s="25"/>
     </row>
-    <row r="7" ht="74.25" spans="2:5">
+    <row r="7" ht="71.5" spans="1:5">
       <c r="B7" s="20" t="s">
         <v>184</v>
       </c>
@@ -9251,7 +9333,7 @@
         <v>341</v>
       </c>
     </row>
-    <row r="8" spans="2:5">
+    <row r="8" spans="1:5">
       <c r="B8" s="20" t="s">
         <v>351</v>
       </c>
@@ -9261,7 +9343,7 @@
       <c r="D8" s="13"/>
       <c r="E8" s="25"/>
     </row>
-    <row r="9" ht="42.95" customHeight="1" spans="2:5">
+    <row r="9" ht="42.95" customHeight="1" spans="1:5">
       <c r="B9" s="20" t="s">
         <v>354</v>
       </c>
@@ -9273,7 +9355,7 @@
       </c>
       <c r="E9" s="25"/>
     </row>
-    <row r="10" spans="2:5">
+    <row r="10" spans="1:5">
       <c r="B10" s="20" t="s">
         <v>356</v>
       </c>
@@ -9283,7 +9365,7 @@
       <c r="D10" s="13"/>
       <c r="E10" s="25"/>
     </row>
-    <row r="11" ht="60.95" customHeight="1" spans="2:5">
+    <row r="11" ht="60.95" customHeight="1" spans="1:5">
       <c r="B11" s="20" t="s">
         <v>357</v>
       </c>
@@ -9293,7 +9375,7 @@
       <c r="D11" s="13"/>
       <c r="E11" s="25"/>
     </row>
-    <row r="12" ht="30" spans="2:5">
+    <row r="12" ht="29" spans="1:5">
       <c r="B12" s="13" t="s">
         <v>359</v>
       </c>
@@ -9305,7 +9387,7 @@
       </c>
       <c r="E12" s="25"/>
     </row>
-    <row r="13" ht="30" spans="2:5">
+    <row r="13" ht="29" spans="1:5">
       <c r="B13" s="13" t="s">
         <v>363</v>
       </c>
@@ -9315,7 +9397,7 @@
       <c r="D13" s="13"/>
       <c r="E13" s="25"/>
     </row>
-    <row r="14" ht="78" customHeight="1" spans="2:5">
+    <row r="14" ht="78" customHeight="1" spans="1:5">
       <c r="B14" s="13" t="s">
         <v>364</v>
       </c>
@@ -9325,7 +9407,7 @@
       <c r="D14" s="13"/>
       <c r="E14" s="25"/>
     </row>
-    <row r="15" ht="45" spans="2:5">
+    <row r="15" ht="43.5" spans="1:5">
       <c r="B15" s="20" t="s">
         <v>251</v>
       </c>
@@ -9337,7 +9419,7 @@
       </c>
       <c r="E15" s="25"/>
     </row>
-    <row r="16" spans="2:5">
+    <row r="16" spans="1:5">
       <c r="B16" s="20" t="s">
         <v>254</v>
       </c>
@@ -9346,7 +9428,7 @@
       </c>
       <c r="E16" s="25"/>
     </row>
-    <row r="17" ht="30" spans="2:5">
+    <row r="17" ht="29" spans="2:5">
       <c r="B17" t="s">
         <v>370</v>
       </c>
@@ -9360,7 +9442,7 @@
         <v>395</v>
       </c>
     </row>
-    <row r="18" customHeight="1" spans="2:5">
+    <row r="18" ht="15" customHeight="1" spans="2:5">
       <c r="B18" s="13" t="s">
         <v>175</v>
       </c>
@@ -9397,14 +9479,14 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:E18"/>
-  <sheetFormatPr defaultColWidth="9.14285714285714" defaultRowHeight="15" outlineLevelCol="4"/>
+  <sheetFormatPr defaultColWidth="9.14545454545454" defaultRowHeight="14.5" outlineLevelCol="4"/>
   <cols>
-    <col min="1" max="1" width="9.14285714285714" customWidth="1"/>
-    <col min="2" max="2" width="23.1428571428571" customWidth="1"/>
-    <col min="3" max="3" width="34.2857142857143" customWidth="1"/>
-    <col min="4" max="4" width="25.1428571428571" customWidth="1"/>
-    <col min="5" max="5" width="33.4285714285714" customWidth="1"/>
-    <col min="6" max="6" width="9.14285714285714" customWidth="1"/>
+    <col min="1" max="1" width="9.14545454545454" customWidth="1"/>
+    <col min="2" max="2" width="23.1454545454545" customWidth="1"/>
+    <col min="3" max="3" width="34.2818181818182" customWidth="1"/>
+    <col min="4" max="4" width="25.1454545454545" customWidth="1"/>
+    <col min="5" max="5" width="33.4272727272727" customWidth="1"/>
+    <col min="6" max="6" width="9.14545454545454" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
@@ -9424,12 +9506,12 @@
         <v>17</v>
       </c>
     </row>
-    <row r="2" spans="1:1">
+    <row r="2" spans="1:5">
       <c r="A2" s="19" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="3" spans="2:3">
+    <row r="3" spans="1:5">
       <c r="B3" s="13" t="s">
         <v>19</v>
       </c>
@@ -9437,7 +9519,7 @@
         <v>397</v>
       </c>
     </row>
-    <row r="4" spans="1:4">
+    <row r="4" spans="1:5">
       <c r="A4" s="19"/>
       <c r="B4" s="20" t="s">
         <v>21</v>
@@ -9460,7 +9542,7 @@
       <c r="D5" s="13"/>
       <c r="E5" s="13"/>
     </row>
-    <row r="6" ht="45" spans="2:5">
+    <row r="6" ht="29" spans="1:5">
       <c r="B6" s="21" t="s">
         <v>27</v>
       </c>
@@ -9470,7 +9552,7 @@
       <c r="D6" s="13"/>
       <c r="E6" s="13"/>
     </row>
-    <row r="7" spans="2:5">
+    <row r="7" spans="1:5">
       <c r="B7" s="20" t="s">
         <v>184</v>
       </c>
@@ -9482,7 +9564,7 @@
       </c>
       <c r="E7" s="22"/>
     </row>
-    <row r="8" ht="165" spans="2:5">
+    <row r="8" ht="159.5" spans="1:5">
       <c r="B8" s="20" t="s">
         <v>351</v>
       </c>
@@ -9494,7 +9576,7 @@
       </c>
       <c r="E8" s="23"/>
     </row>
-    <row r="9" spans="2:3">
+    <row r="9" spans="1:5">
       <c r="B9" s="20" t="s">
         <v>354</v>
       </c>
@@ -9502,7 +9584,7 @@
         <v>403</v>
       </c>
     </row>
-    <row r="10" spans="2:3">
+    <row r="10" spans="1:5">
       <c r="B10" s="20" t="s">
         <v>356</v>
       </c>
@@ -9510,7 +9592,7 @@
         <v>404</v>
       </c>
     </row>
-    <row r="11" spans="2:3">
+    <row r="11" spans="1:5">
       <c r="B11" t="s">
         <v>357</v>
       </c>
@@ -9518,7 +9600,7 @@
         <v>405</v>
       </c>
     </row>
-    <row r="12" ht="90" spans="2:4">
+    <row r="12" ht="87" spans="1:5">
       <c r="B12" s="20" t="s">
         <v>251</v>
       </c>
@@ -9529,7 +9611,7 @@
         <v>253</v>
       </c>
     </row>
-    <row r="13" ht="45" spans="2:3">
+    <row r="13" ht="29" spans="1:5">
       <c r="B13" s="20" t="s">
         <v>254</v>
       </c>
@@ -9537,7 +9619,7 @@
         <v>255</v>
       </c>
     </row>
-    <row r="14" ht="75" spans="2:4">
+    <row r="14" ht="72.5" spans="1:5">
       <c r="B14" s="20" t="s">
         <v>367</v>
       </c>
@@ -9548,7 +9630,7 @@
         <v>407</v>
       </c>
     </row>
-    <row r="15" ht="90" spans="2:4">
+    <row r="15" ht="87" spans="1:5">
       <c r="B15" t="s">
         <v>408</v>
       </c>
@@ -9559,7 +9641,7 @@
         <v>410</v>
       </c>
     </row>
-    <row r="16" spans="2:3">
+    <row r="16" spans="1:5">
       <c r="B16" t="s">
         <v>411</v>
       </c>
@@ -9567,7 +9649,7 @@
         <v>412</v>
       </c>
     </row>
-    <row r="17" customHeight="1" spans="2:4">
+    <row r="17" ht="15" customHeight="1" spans="2:4">
       <c r="B17" s="13" t="s">
         <v>175</v>
       </c>
@@ -9578,7 +9660,7 @@
         <v>413</v>
       </c>
     </row>
-    <row r="18" ht="30" spans="2:4">
+    <row r="18" ht="29" spans="2:4">
       <c r="B18" s="13" t="s">
         <v>178</v>
       </c>
